--- a/data/trans_bre/IP13-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP13-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>2,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>62,69%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; -0,04</t>
+          <t>-7,81; -0,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 5,31</t>
+          <t>-4,37; 6,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 9,53</t>
+          <t>-0,5; 9,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 7,56</t>
+          <t>-2,11; 7,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-94,09; 26,4</t>
+          <t>-92,82; 37,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-79,81; 309,89</t>
+          <t>-74,21; 419,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-49,97; 1307,89</t>
+          <t>-43,38; 1231,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,74; 405,18</t>
+          <t>-47,86; 427,49</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,0</t>
+          <t>-4,54</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-43,02%</t>
+          <t>-47,18%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 4,15</t>
+          <t>-6,25; 4,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 11,02</t>
+          <t>0,09; 10,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 0,72</t>
+          <t>-6,9; 0,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 2,91</t>
+          <t>-11,49; 1,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-77,12; 175,99</t>
+          <t>-77,82; 180,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 988,68</t>
+          <t>-32,47; 985,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 59,48</t>
+          <t>-92,1; 66,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-79,44; 66,88</t>
+          <t>-82,08; 51,99</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,06%</t>
+          <t>-20,27%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 8,38</t>
+          <t>-2,34; 8,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 8,0</t>
+          <t>-3,3; 8,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 6,78</t>
+          <t>-7,69; 6,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 6,48</t>
+          <t>-8,15; 5,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-64,91; 473,49</t>
+          <t>-61,91; 558,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-62,59; 409,46</t>
+          <t>-54,97; 402,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-74,87; 210,94</t>
+          <t>-75,62; 213,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-78,58; 269,33</t>
+          <t>-84,8; 241,37</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,2</t>
+          <t>-1,98</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-43,94%</t>
+          <t>-28,46%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 3,5</t>
+          <t>-4,08; 3,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,38; -0,68</t>
+          <t>-8,02; -0,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 6,96</t>
+          <t>-0,32; 6,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 0,85</t>
+          <t>-5,88; 1,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,75; 92,02</t>
+          <t>-53,38; 94,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,67; -2,1</t>
+          <t>-73,14; 2,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 226,84</t>
+          <t>-7,4; 237,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,97; 18,93</t>
+          <t>-65,82; 35,98</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 3,21</t>
+          <t>-5,3; 3,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 6,91</t>
+          <t>-1,98; 6,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 2,88</t>
+          <t>-4,42; 2,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 8,49</t>
+          <t>-3,55; 6,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-78,39; 138,22</t>
+          <t>-84,4; 143,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,14; 223,0</t>
+          <t>-32,04; 251,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-77,56; 134,22</t>
+          <t>-72,74; 123,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 223,3</t>
+          <t>-44,57; 172,14</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 3,17</t>
+          <t>-8,51; 3,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,01; -0,06</t>
+          <t>-11,64; -0,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 6,39</t>
+          <t>-4,25; 6,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 6,78</t>
+          <t>-6,36; 6,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-84,11; 116,78</t>
+          <t>-82,58; 133,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 217,88</t>
+          <t>-100,0; 131,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,19; 450,02</t>
+          <t>-78,73; 413,78</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-8,54%</t>
+          <t>-7,44%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 0,89</t>
+          <t>-2,69; 1,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,78</t>
+          <t>-2,37; 1,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,91</t>
+          <t>-1,02; 2,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,88</t>
+          <t>-2,8; 1,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,08; 20,34</t>
+          <t>-44,02; 27,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 36,73</t>
+          <t>-34,25; 37,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 86,23</t>
+          <t>-20,35; 87,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-36,25; 35,48</t>
+          <t>-35,86; 29,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP13-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP13-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-3,53</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,79</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,55</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-65,43%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>174,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>62,69%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-3.527678161499783</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7414423027993444</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.792008447694657</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.550834759301469</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.6542914219198506</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1861453307235638</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.741553813574073</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.6268953899815826</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-7,81; -0,04</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,37; 6,37</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-0,5; 9,68</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 7,99</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-92,82; 37,34</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-74,21; 419,61</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-43,38; 1231,48</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-47,86; 427,49</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-7.811765201037292</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.374424056832813</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.4989971604720357</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.111309389976042</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.9282053154820508</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.7421279813761656</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.4338264492088199</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4786078124163007</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>-0.04260257487396599</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.367966147605967</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.682312986155292</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.985157245165558</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.3733537299592881</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>4.196105616344657</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>12.31483855251667</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>4.274893743321677</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,23</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,84</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-4,54</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-15,68%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>172,45%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-61,8%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-47,18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,25; 4,59</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 10,85</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-6,9; 0,55</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-11,49; 1,4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-77,82; 180,85</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-32,47; 985,97</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-92,1; 66,43</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-82,08; 51,99</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.825560369878249</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>5.230875841721951</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.84385397203138</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-4.535194419380314</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1568041389928451</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.72449860117234</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.6179594314996291</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.4718243562740199</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,52</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,23</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>74,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>42,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-7,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-20,27%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.248156137046472</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.09254008683033914</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-6.904934581826254</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-11.48558186526934</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.7782033477008448</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3246703102851626</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.9209863128924505</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.820794233191139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,34; 8,83</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,3; 8,34</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-7,69; 6,44</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-8,15; 5,12</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-61,91; 558,65</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-54,97; 402,17</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-75,62; 213,38</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-84,8; 241,37</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.586870160385371</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>10.85142712310076</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5525106697867436</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.395404250357769</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.80851792219003</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>9.85967841755518</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.6643157192231391</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.5199035028523635</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-4,16</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,21</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,98</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-2,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-48,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>70,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-28,46%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.522537773608461</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.927937400284414</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.506022295033564</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.2283510307125</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.7409544418425256</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.4228666102344856</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.07586724770645897</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.2026813112757272</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,08; 3,6</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-8,02; -0,14</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,32; 6,86</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-5,88; 1,7</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-53,38; 94,71</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-73,14; 2,28</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-7,4; 237,06</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-65,82; 35,98</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.344070930329316</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.302123062145844</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.694857160873006</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-8.149550668805443</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6191235501143789</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5497389822373521</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.7561939659070747</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.8480152476589791</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.829934853908982</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.344070229667448</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.443713411006325</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.116624481535935</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>5.586474026605212</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>4.021656264553003</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2.133780654772305</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.41372435501646</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-27,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>44,47%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-14,1%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>30,61%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,3; 3,03</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,98; 6,88</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-4,42; 2,95</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-3,55; 6,62</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-84,4; 143,22</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-32,04; 251,54</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-72,74; 123,27</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-44,57; 172,14</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.1324034131485574</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-4.163261054841135</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>3.207947306373113</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.977504041412688</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.02423683008729792</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.4859815382755209</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.7027771880192732</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2846498181019159</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-2,84</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-6,12</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,68</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-39,74%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-79,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.075713364815815</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-8.02191829166726</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.3161514425138098</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.883397378294299</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5338456121415154</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7314293931957437</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.07395357051837141</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6582127835467538</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-8,51; 3,25</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-11,64; -0,14</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-4,25; 6,82</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-6,36; 6,84</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-82,58; 133,49</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 131,53</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-78,73; 413,78</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.600321752299401</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-0.1386822584400425</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.85782903645588</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.697873104178047</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.9470846576698978</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.02279886959437278</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.370619660530501</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3597938120005478</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,295 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-17,27%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-5,67%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,5%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-7,44%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-1.287364046830906</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.191072920473401</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.5972686302399937</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.933446614252894</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2700221554107517</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.4447432658712857</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1410005613635284</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.3060996999020097</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,69; 1,14</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-2,37; 1,81</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,02; 2,84</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-2,8; 1,51</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-44,02; 27,22</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-34,25; 37,75</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-20,35; 87,28</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-35,86; 29,54</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.304092453254173</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.98253240663773</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4.42148473396466</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.549077597232673</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.8440236866893208</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3203543078220604</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.7274203562918691</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.4456768631602799</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>3.027317793308435</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>6.881651225834036</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.946129392951056</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6.623583704322625</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.432155828929426</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2.515442122470243</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.232651844392853</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.721353054007452</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-2.840804107580428</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-6.115509473422765</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.678787663055884</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.2864607997213796</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.3973853693953752</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.7994171763188699</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.215917616431779</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.05607760876476808</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-8.508523746002645</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-11.64376766113213</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-4.249281339747879</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-6.358332627460282</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.825786050788173</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.7873132732354807</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>3.247078402947648</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-0.13954471983966</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>6.823892759627478</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>6.840833139915612</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1.334867286478621</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.315288538644027</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="n">
+        <v>4.137826004222995</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.8943073016440123</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.3372141988376258</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.000103318783054</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.4759988784584411</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.1727061349704905</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.05668132695431637</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.2349543994567253</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.07438049330485044</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-2.690141637565774</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.371533364024301</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.016808378811496</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-2.797421297635247</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.440168401371183</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.342489327559198</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.2034954012031471</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.3586159893925595</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.144991743123826</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.811677189097957</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2.843351435374418</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.507194267535265</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.2721685009285562</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.3774814857444498</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.8727954833817196</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.2953906852080553</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1315,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
